--- a/output/pdf_financials_xlsx/GMC.xlsx
+++ b/output/pdf_financials_xlsx/GMC.xlsx
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.200975</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.202873</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.235707</v>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>1.362331</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.262291</v>
+        <v>0.045173</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0.690259</v>
@@ -3690,7 +3690,11 @@
           <t>Reserve 10 1,211,169</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -4262,7 +4266,11 @@
           <t>Reserve 10</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>1.200975</v>
       </c>
@@ -5740,7 +5748,11 @@
           <t>Prepaid exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GMC.xlsx
+++ b/output/pdf_financials_xlsx/GMC.xlsx
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.197794</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.192633</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.006449</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.197794</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.024</v>
+        <v>0.216633</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.051932</v>
+        <v>0.058381</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.202961</v>
+        <v>0.005167</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.39567</v>
+        <v>0.203037</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.015065</v>
+        <v>0.008616</v>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">

--- a/output/pdf_financials_xlsx/GMC.xlsx
+++ b/output/pdf_financials_xlsx/GMC.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.151409</v>
+        <v>0.205409</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.157766</v>
+        <v>0.205766</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.157815</v>
+        <v>0.202815</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.205536</v>
+        <v>0.221536</v>
       </c>
     </row>
     <row r="8">
@@ -1713,18 +1713,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.287572</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.234057</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.402682</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0.527404</v>
       </c>
     </row>
     <row r="65">
@@ -1784,10 +1782,8 @@
       <c r="D67" s="3" t="n">
         <v>0.525462</v>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="3" t="n">
+        <v>0.567559</v>
       </c>
     </row>
     <row r="68">
@@ -1797,7 +1793,7 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.346492</v>
+        <v>0.634064</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.737376</v>
@@ -6312,7 +6308,11 @@
           <t>Directors’ fees 11</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E88" s="5" t="n">
         <v>0.054</v>
       </c>
